--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS6403_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS6403_SW2.xlsx
@@ -949,7 +949,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>Air-Way FF7403 (s18, double-pass 2026-10-15, parts.air-way.com/api/series/18, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6403-04-04 (ORFS-p005-t05) | MODEL: L41 face -&gt; JIC tip, hex S1, bores D (JIC side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male JIC end MS33656J (2403 table, VERIFIED vs Brennan); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF7403 (s18, double-pass 2026-10-15, parts.air-way.com/api/series/18, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6403-04-04 (ORFS-p005-t05) | MODEL: L41 face -&gt; JIC tip, hex S1, bores D (JIC side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male JIC end MS33656J (2403 table, VERIFIED vs Brennan); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>Air-Way FF7403 (s18, double-pass 2026-10-15, parts.air-way.com/api/series/18, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6403-06-06 (ORFS-p005-t05) | MODEL: L41 face -&gt; JIC tip, hex S1, bores D (JIC side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male JIC end MS33656J (2403 table, VERIFIED vs Brennan); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF7403 (s18, double-pass 2026-10-15, parts.air-way.com/api/series/18, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6403-06-06 (ORFS-p005-t05) | MODEL: L41 face -&gt; JIC tip, hex S1, bores D (JIC side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male JIC end MS33656J (2403 table, VERIFIED vs Brennan); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>Air-Way FF7403 (s18, double-pass 2026-10-15, parts.air-way.com/api/series/18, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6403-10-10 (ORFS-p006-t01) | MODEL: L41 face -&gt; JIC tip, hex S1, bores D (JIC side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male JIC end MS33656J (2403 table, VERIFIED vs Brennan); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF7403 (s18, double-pass 2026-10-15, parts.air-way.com/api/series/18, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6403-10-10 (ORFS-p006-t01) | MODEL: L41 face -&gt; JIC tip, hex S1, bores D (JIC side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male JIC end MS33656J (2403 table, VERIFIED vs Brennan); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>Air-Way FF7403 (s18, double-pass 2026-10-15, parts.air-way.com/api/series/18, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6403-12-12 (ORFS-p006-t01) | MODEL: L41 face -&gt; JIC tip, hex S1, bores D (JIC side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male JIC end MS33656J (2403 table, VERIFIED vs Brennan); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF7403 (s18, double-pass 2026-10-15, parts.air-way.com/api/series/18, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6403-12-12 (ORFS-p006-t01) | MODEL: L41 face -&gt; JIC tip, hex S1, bores D (JIC side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male JIC end MS33656J (2403 table, VERIFIED vs Brennan); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>Air-Way FF7403 (s18, double-pass 2026-10-15, parts.air-way.com/api/series/18, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6403-16-16 (ORFS-p006-t01) | MODEL: L41 face -&gt; JIC tip, hex S1, bores D (JIC side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male JIC end MS33656J (2403 table, VERIFIED vs Brennan); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF7403 (s18, double-pass 2026-10-15, parts.air-way.com/api/series/18, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6403-16-16 (ORFS-p006-t01) | MODEL: L41 face -&gt; JIC tip, hex S1, bores D (JIC side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male JIC end MS33656J (2403 table, VERIFIED vs Brennan); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>Air-Way FF7403 (s18, double-pass 2026-10-15, parts.air-way.com/api/series/18, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6403-20-20 (ORFS-p006-t01) | MODEL: L41 face -&gt; JIC tip, hex S1, bores D (JIC side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male JIC end MS33656J (2403 table, VERIFIED vs Brennan); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF7403 (s18, double-pass 2026-10-15, parts.air-way.com/api/series/18, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6403-20-20 (ORFS-p006-t01) | MODEL: L41 face -&gt; JIC tip, hex S1, bores D (JIC side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male JIC end MS33656J (2403 table, VERIFIED vs Brennan); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
